--- a/spectra_2026/data/tipsToAdd_2026-10-30.xlsx
+++ b/spectra_2026/data/tipsToAdd_2026-10-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahipp\Documents\github\fagaceae-phylo\spectra_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7173C42-B64D-4AB2-B387-C84DE52A0B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF0BD7A-6923-4A59-AAA4-741CF13C048A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" firstSheet="1" activeTab="3" xr2:uid="{1BAB3139-B2FE-4142-947A-295D6A02B330}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="765">
   <si>
     <t>Fagus_grandifolia</t>
   </si>
@@ -2308,9 +2308,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Removed- we're unsure what our samples really are.</t>
-  </si>
-  <si>
     <t>syn Q. pumila Walt. (Oaks of the World 2026- -- "The name Q.elliottii has been given to Q.pumila by Wilbur in 2002 under the pretext that the latin diagnosis made by Walter in 1788 was not complete, but the neotype choosen by Wilbur is actually a hybrid between Q.falcata and Q.phellos.") Also note there's some homonyms of Q. pumila too. We have several and in my database they've gone from Q. pumila to Q. elliotii and then back to Q. pumila since we started the rad-seq project. Q. ellioti is a spelling variant.</t>
   </si>
   <si>
@@ -2327,6 +2324,21 @@
   </si>
   <si>
     <t xml:space="preserve">? Isn't this in the tree? I'm not seeing it in the above choices...Oaks of the world have this as syn to Q. Mongolica subsp crispula. SYST-MOR-0006366.wRE is currented determined as Q. mongolica var. grosserserrata. Oaks of the world has that also as syn to Q. mongolica subsp. Crispula. So  if we agree with the above statements, then we have this sequenced. </t>
+  </si>
+  <si>
+    <t>Quercus_mongolica_var._grosseserrata</t>
+  </si>
+  <si>
+    <t>NO ADDITION. Removed- we're unsure what our samples really are.</t>
+  </si>
+  <si>
+    <t>NO ADDITION. Can weld onto phylogeny</t>
+  </si>
+  <si>
+    <t>NO ADDITION. Spelling variant.</t>
+  </si>
+  <si>
+    <t>FIXED IN SPECTRAL DATA SHEET: Spelling variant. Quercus martinezii, which we should have in phylo. My memory is that some of these may not have sequenced as well as other samples, so potential that it could have been dropped.</t>
   </si>
 </sst>
 </file>
@@ -6698,7 +6710,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" ht="44.25" x14ac:dyDescent="0.75">
       <c r="A8" s="7" t="s">
         <v>459</v>
       </c>
@@ -6706,7 +6718,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>45</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.75">
@@ -7281,7 +7293,7 @@
         <v>445</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.75">
@@ -7377,7 +7389,7 @@
         <v>448</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.75">
@@ -7801,7 +7813,7 @@
         <v>11</v>
       </c>
       <c r="D218" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.75">
@@ -8267,7 +8279,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="305" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C305" t="s">
         <v>0</v>
       </c>
@@ -8275,7 +8287,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="306" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C306" t="s">
         <v>1</v>
       </c>
@@ -8283,23 +8295,29 @@
         <v>34</v>
       </c>
     </row>
-    <row r="307" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C307" t="s">
         <v>444</v>
       </c>
       <c r="D307" s="10" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="308" spans="3:4" ht="73.75" x14ac:dyDescent="0.75">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="73.75" x14ac:dyDescent="0.75">
+      <c r="A308" t="s">
+        <v>760</v>
+      </c>
+      <c r="B308" t="s">
+        <v>7</v>
+      </c>
       <c r="C308" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D308" s="11" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="309" spans="3:4" x14ac:dyDescent="0.75">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C309" t="s">
         <v>8</v>
       </c>
@@ -8307,7 +8325,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="310" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C310" t="s">
         <v>9</v>
       </c>
@@ -8315,15 +8333,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="311" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C311" t="s">
         <v>446</v>
       </c>
       <c r="D311" s="10" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="312" spans="3:4" x14ac:dyDescent="0.75">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C312" t="s">
         <v>10</v>
       </c>
@@ -8331,23 +8349,23 @@
         <v>39</v>
       </c>
     </row>
-    <row r="313" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C313" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D313" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="314" spans="3:4" x14ac:dyDescent="0.75">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C314" t="s">
         <v>13</v>
       </c>
       <c r="D314" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="315" spans="3:4" ht="73.75" x14ac:dyDescent="0.75">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="73.75" x14ac:dyDescent="0.75">
       <c r="C315" s="8" t="s">
         <v>14</v>
       </c>
@@ -8355,7 +8373,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="316" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C316" t="s">
         <v>15</v>
       </c>
@@ -8363,7 +8381,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="317" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C317" t="s">
         <v>16</v>
       </c>
@@ -8371,15 +8389,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="318" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C318" t="s">
         <v>449</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="319" spans="3:4" x14ac:dyDescent="0.75">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C319" t="s">
         <v>22</v>
       </c>
@@ -8387,7 +8405,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="320" spans="3:4" x14ac:dyDescent="0.75">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.75">
       <c r="C320" t="s">
         <v>25</v>
       </c>
